--- a/artfynd/A 23619-2024 artfynd.xlsx
+++ b/artfynd/A 23619-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119694330</v>
+        <v>119694369</v>
       </c>
       <c r="B2" t="n">
         <v>91840</v>
@@ -708,16 +708,8 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -726,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>536416</v>
+        <v>536420</v>
       </c>
       <c r="R2" t="n">
-        <v>6674736</v>
+        <v>6674733</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -789,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119694369</v>
+        <v>119694330</v>
       </c>
       <c r="B3" t="n">
         <v>91840</v>
@@ -822,8 +814,16 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>536420</v>
+        <v>536416</v>
       </c>
       <c r="R3" t="n">
-        <v>6674733</v>
+        <v>6674736</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>

--- a/artfynd/A 23619-2024 artfynd.xlsx
+++ b/artfynd/A 23619-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119694369</v>
+        <v>119694330</v>
       </c>
       <c r="B2" t="n">
         <v>91840</v>
@@ -708,8 +708,16 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -718,10 +726,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>536420</v>
+        <v>536416</v>
       </c>
       <c r="R2" t="n">
-        <v>6674733</v>
+        <v>6674736</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,7 +789,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119694330</v>
+        <v>119694369</v>
       </c>
       <c r="B3" t="n">
         <v>91840</v>
@@ -814,16 +822,8 @@
           <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>536416</v>
+        <v>536420</v>
       </c>
       <c r="R3" t="n">
-        <v>6674736</v>
+        <v>6674733</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>

--- a/artfynd/A 23619-2024 artfynd.xlsx
+++ b/artfynd/A 23619-2024 artfynd.xlsx
@@ -678,16 +678,11 @@
         <v>119694330</v>
       </c>
       <c r="B2" t="n">
-        <v>91840</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -792,16 +787,11 @@
         <v>119694369</v>
       </c>
       <c r="B3" t="n">
-        <v>91840</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -898,12 +888,7 @@
         <v>119694287</v>
       </c>
       <c r="B4" t="n">
-        <v>97907</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 23619-2024 artfynd.xlsx
+++ b/artfynd/A 23619-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -781,6 +786,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119694330</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -882,6 +892,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119694369</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -984,8 +999,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119694287</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>